--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B251"/>
+  <dimension ref="A1:B252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3426,6 +3426,18 @@
         </is>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B252"/>
+  <dimension ref="A1:B253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3438,6 +3438,18 @@
         </is>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B253"/>
+  <dimension ref="A1:B254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3450,6 +3450,18 @@
         </is>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B254"/>
+  <dimension ref="A1:B255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3462,6 +3462,18 @@
         </is>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B255"/>
+  <dimension ref="A1:B256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3474,6 +3474,18 @@
         </is>
       </c>
     </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B256"/>
+  <dimension ref="A1:B257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3486,6 +3486,18 @@
         </is>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B257"/>
+  <dimension ref="A1:B258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3498,6 +3498,18 @@
         </is>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B258"/>
+  <dimension ref="A1:B259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3510,6 +3510,18 @@
         </is>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B259"/>
+  <dimension ref="A1:B260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3522,6 +3522,18 @@
         </is>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B260"/>
+  <dimension ref="A1:B261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3534,6 +3534,18 @@
         </is>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B261"/>
+  <dimension ref="A1:B262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3546,6 +3546,18 @@
         </is>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B262"/>
+  <dimension ref="A1:B263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3558,6 +3558,18 @@
         </is>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B263"/>
+  <dimension ref="A1:B264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3570,6 +3570,18 @@
         </is>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B264"/>
+  <dimension ref="A1:B265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3582,6 +3582,18 @@
         </is>
       </c>
     </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B265"/>
+  <dimension ref="A1:B266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3594,6 +3594,18 @@
         </is>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B266"/>
+  <dimension ref="A1:B267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3606,6 +3606,18 @@
         </is>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B267"/>
+  <dimension ref="A1:B268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3618,6 +3618,18 @@
         </is>
       </c>
     </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B268"/>
+  <dimension ref="A1:B269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3630,6 +3630,18 @@
         </is>
       </c>
     </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B269"/>
+  <dimension ref="A1:B270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3642,6 +3642,18 @@
         </is>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B270"/>
+  <dimension ref="A1:B271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3654,6 +3654,18 @@
         </is>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B271"/>
+  <dimension ref="A1:B272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3666,6 +3666,18 @@
         </is>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B272"/>
+  <dimension ref="A1:B273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3678,6 +3678,18 @@
         </is>
       </c>
     </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B273"/>
+  <dimension ref="A1:B274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3690,6 +3690,18 @@
         </is>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B274"/>
+  <dimension ref="A1:B275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3702,6 +3702,18 @@
         </is>
       </c>
     </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B275"/>
+  <dimension ref="A1:B276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3714,6 +3714,18 @@
         </is>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2.20							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B276"/>
+  <dimension ref="A1:B277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3726,6 +3726,18 @@
         </is>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>1.20							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B277"/>
+  <dimension ref="A1:B278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3738,6 +3738,18 @@
         </is>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>19.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B278"/>
+  <dimension ref="A1:B279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3750,6 +3750,18 @@
         </is>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>3.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B279"/>
+  <dimension ref="A1:B280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3762,6 +3762,18 @@
         </is>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B280"/>
+  <dimension ref="A1:B281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3774,6 +3774,18 @@
         </is>
       </c>
     </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B281"/>
+  <dimension ref="A1:B282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3786,6 +3786,18 @@
         </is>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B282"/>
+  <dimension ref="A1:B283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3798,6 +3798,18 @@
         </is>
       </c>
     </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B283"/>
+  <dimension ref="A1:B284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3810,6 +3810,18 @@
         </is>
       </c>
     </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B284"/>
+  <dimension ref="A1:B285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3822,6 +3822,18 @@
         </is>
       </c>
     </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>0.20							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B285"/>
+  <dimension ref="A1:B286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3834,6 +3834,18 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B286"/>
+  <dimension ref="A1:B287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3846,6 +3846,18 @@
         </is>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B287"/>
+  <dimension ref="A1:B288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3858,6 +3858,18 @@
         </is>
       </c>
     </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B288"/>
+  <dimension ref="A1:B289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3870,6 +3870,18 @@
         </is>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>48.80							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B289"/>
+  <dimension ref="A1:B290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3882,6 +3882,18 @@
         </is>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2.20							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B290"/>
+  <dimension ref="A1:B291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3894,6 +3894,18 @@
         </is>
       </c>
     </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B291"/>
+  <dimension ref="A1:B292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3906,6 +3906,18 @@
         </is>
       </c>
     </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>1.20							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B292"/>
+  <dimension ref="A1:B293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3918,6 +3918,18 @@
         </is>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B293"/>
+  <dimension ref="A1:B294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3930,6 +3930,18 @@
         </is>
       </c>
     </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B294"/>
+  <dimension ref="A1:B295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3942,6 +3942,18 @@
         </is>
       </c>
     </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B295"/>
+  <dimension ref="A1:B296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3954,6 +3954,18 @@
         </is>
       </c>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pioggia.xlsx
+++ b/pioggia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B296"/>
+  <dimension ref="A1:B297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3966,6 +3966,18 @@
         </is>
       </c>
     </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>0.00							mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
